--- a/TestData/TMTT0038098_VerifyTheFunctionalityOfPortfolioValuationOnOpportunityDetailPage.xlsx
+++ b/TestData/TMTT0038098_VerifyTheFunctionalityOfPortfolioValuationOnOpportunityDetailPage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4777DE27-4C85-479B-AD25-8AEC07502CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F189B2-71CC-4E1F-80CB-483B26B51B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>AdditonalSubject</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -307,6 +304,9 @@
   </si>
   <si>
     <t>FA - Portfolio-Valuation</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -709,153 +709,153 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="T1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="X1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="AA1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" t="s">
+        <v>83</v>
+      </c>
+      <c r="W2" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" t="s">
         <v>82</v>
       </c>
-      <c r="B2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>81</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>86</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="U2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="AB2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -875,18 +875,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -910,54 +910,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -997,138 +997,138 @@
   <sheetData>
     <row r="1" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="T1" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="U1" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="V2" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="W2" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">

--- a/TestData/TMTT0038098_VerifyTheFunctionalityOfPortfolioValuationOnOpportunityDetailPage.xlsx
+++ b/TestData/TMTT0038098_VerifyTheFunctionalityOfPortfolioValuationOnOpportunityDetailPage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F189B2-71CC-4E1F-80CB-483B26B51B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEDC0BE-D4FB-4C87-AE87-8D1A74FAFA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>Client</t>
   </si>
@@ -307,6 +307,12 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>2nd Staff</t>
+  </si>
+  <si>
+    <t>Drew Koecher</t>
   </si>
 </sst>
 </file>
@@ -662,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -684,9 +690,10 @@
     <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -771,8 +778,11 @@
       <c r="AB1" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC1" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>81</v>
       </c>
@@ -856,6 +866,9 @@
       </c>
       <c r="AB2" s="3" t="s">
         <v>37</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0038098_VerifyTheFunctionalityOfPortfolioValuationOnOpportunityDetailPage.xlsx
+++ b/TestData/TMTT0038098_VerifyTheFunctionalityOfPortfolioValuationOnOpportunityDetailPage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEDC0BE-D4FB-4C87-AE87-8D1A74FAFA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859FCD83-F800-40EE-B2C7-D0D81C58E68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,9 +51,6 @@
     <t>AdditonalSubject</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -313,13 +310,16 @@
   </si>
   <si>
     <t>Drew Koecher</t>
+  </si>
+  <si>
+    <t>CSDN-0000000550</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,6 +337,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -359,10 +367,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -388,8 +397,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -716,164 +727,167 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="T1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="X1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="AA1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="AC1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="U2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y2" t="s">
         <v>81</v>
       </c>
-      <c r="B2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>85</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R2" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="U2" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="W2" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="AB2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://hl--test.sandbox.lightning.force.com/lightning/r/Coverage_Sector_Dependency__c/a516e0000000gsuAAA/view" xr:uid="{6202CCC7-A86C-4CCE-BBC7-3C9194D63E20}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -888,18 +902,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -923,54 +937,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1010,138 +1024,138 @@
   <sheetData>
     <row r="1" spans="1:23" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="F1" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="T1" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="U1" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="U2" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="V2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="W2" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="U2" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">

--- a/TestData/TMTT0038098_VerifyTheFunctionalityOfPortfolioValuationOnOpportunityDetailPage.xlsx
+++ b/TestData/TMTT0038098_VerifyTheFunctionalityOfPortfolioValuationOnOpportunityDetailPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859FCD83-F800-40EE-B2C7-D0D81C58E68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F031F0-5A9C-49C5-98D8-8E632CDE2A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -297,29 +297,29 @@
     <t>Techno Alpha</t>
   </si>
   <si>
-    <t> Liz Hedgcock</t>
-  </si>
-  <si>
     <t>FA - Portfolio-Valuation</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>2nd Staff</t>
   </si>
   <si>
     <t>Drew Koecher</t>
   </si>
   <si>
-    <t>CSDN-0000000550</t>
+    <t>HC - Healthcare</t>
+  </si>
+  <si>
+    <t>Dental</t>
+  </si>
+  <si>
+    <t>Liz Hedgcock</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,14 +337,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -367,11 +359,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -397,10 +388,8 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -790,7 +779,7 @@
         <v>44</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
@@ -801,13 +790,13 @@
         <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>93</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -879,7 +868,7 @@
         <v>36</v>
       </c>
       <c r="AC2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -913,7 +902,7 @@
         <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTT0038098_VerifyTheFunctionalityOfPortfolioValuationOnOpportunityDetailPage.xlsx
+++ b/TestData/TMTT0038098_VerifyTheFunctionalityOfPortfolioValuationOnOpportunityDetailPage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F031F0-5A9C-49C5-98D8-8E632CDE2A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88477A11-DBEE-400E-80EF-DA8C45ACC0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -312,7 +312,7 @@
     <t>Dental</t>
   </si>
   <si>
-    <t>Liz Hedgcock</t>
+    <t>Danielle Morello</t>
   </si>
 </sst>
 </file>
